--- a/Matrice_Horaires_Roulements_Agents.xlsx
+++ b/Matrice_Horaires_Roulements_Agents.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="1" r:id="R98c87bd5ae544eff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agents" sheetId="2" r:id="Rafd59c126dd44b56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horaires annuels" sheetId="3" r:id="Rb08c388da01d4476"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roulements" sheetId="4" r:id="R4afc8f17f2274042"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exemple" sheetId="5" r:id="R436988276c7843ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode d'emploi" sheetId="1" r:id="R55010974d175493a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agents" sheetId="2" r:id="R25f7ed48b79f4a21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horaires annuels" sheetId="3" r:id="R6d06be80f6a54677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roulements" sheetId="4" r:id="Rb2586c8e74384e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exemple" sheetId="5" r:id="Re33e84b1d5354996"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +57,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +87,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF5B9BD5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -201,7 +206,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -411,6 +416,11 @@
     <x:xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -421,7 +431,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -431,7 +441,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -441,7 +451,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -451,7 +461,7 @@
         <x:color rgb="FF006100"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -560,9 +570,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -835,14 +845,26 @@
       <x:c r="H13" s="38"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="39"/>
-      <x:c r="B14" s="40"/>
+      <x:c r="A14" s="103" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B14" s="88" t="str">
+        <x:v>Dans « Agents », renseignez Permanence début, Permanence fin et Permanence pause (minutes).</x:v>
+      </x:c>
       <x:c r="C14" s="40"/>
       <x:c r="D14" s="40"/>
       <x:c r="E14" s="40"/>
       <x:c r="F14" s="40"/>
       <x:c r="G14" s="40"/>
       <x:c r="H14" s="41"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="20" t="str">
+        <x:v>Priorité horaire théorique</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>Permanence &gt; Roulement &gt; Standard.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -865,6 +887,9 @@
     <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="10" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="20" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -888,6 +913,15 @@
       </x:c>
       <x:c r="G1" s="65" t="str">
         <x:v>Actif</x:v>
+      </x:c>
+      <x:c r="H1" s="102" t="str">
+        <x:v>Permanence début</x:v>
+      </x:c>
+      <x:c r="I1" s="102" t="str">
+        <x:v>Permanence fin</x:v>
+      </x:c>
+      <x:c r="J1" s="102" t="str">
+        <x:v>Permanence pause (minutes)</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -900,6 +934,11 @@
       <x:c r="G2" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H2" t="str"/>
+      <x:c r="I2" t="str"/>
+      <x:c r="J2" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="31" t="str"/>
@@ -911,6 +950,11 @@
       <x:c r="G3" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H3" t="str"/>
+      <x:c r="I3" t="str"/>
+      <x:c r="J3" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="31" t="str"/>
@@ -922,6 +966,11 @@
       <x:c r="G4" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H4" t="str"/>
+      <x:c r="I4" t="str"/>
+      <x:c r="J4" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="31" t="str"/>
@@ -933,6 +982,11 @@
       <x:c r="G5" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H5" t="str"/>
+      <x:c r="I5" t="str"/>
+      <x:c r="J5" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="31" t="str"/>
@@ -944,6 +998,11 @@
       <x:c r="G6" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H6" t="str"/>
+      <x:c r="I6" t="str"/>
+      <x:c r="J6" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="31" t="str"/>
@@ -955,6 +1014,11 @@
       <x:c r="G7" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H7" t="str"/>
+      <x:c r="I7" t="str"/>
+      <x:c r="J7" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="31" t="str"/>
@@ -966,6 +1030,11 @@
       <x:c r="G8" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H8" t="str"/>
+      <x:c r="I8" t="str"/>
+      <x:c r="J8" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="31" t="str"/>
@@ -977,6 +1046,11 @@
       <x:c r="G9" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H9" t="str"/>
+      <x:c r="I9" t="str"/>
+      <x:c r="J9" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="31" t="str"/>
@@ -988,6 +1062,11 @@
       <x:c r="G10" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H10" t="str"/>
+      <x:c r="I10" t="str"/>
+      <x:c r="J10" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="31" t="str"/>
@@ -999,6 +1078,11 @@
       <x:c r="G11" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H11" t="str"/>
+      <x:c r="I11" t="str"/>
+      <x:c r="J11" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="31" t="str"/>
@@ -1010,6 +1094,11 @@
       <x:c r="G12" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H12" t="str"/>
+      <x:c r="I12" t="str"/>
+      <x:c r="J12" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="31" t="str"/>
@@ -1021,6 +1110,11 @@
       <x:c r="G13" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H13" t="str"/>
+      <x:c r="I13" t="str"/>
+      <x:c r="J13" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="31" t="str"/>
@@ -1032,6 +1126,11 @@
       <x:c r="G14" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H14" t="str"/>
+      <x:c r="I14" t="str"/>
+      <x:c r="J14" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="31" t="str"/>
@@ -1043,6 +1142,11 @@
       <x:c r="G15" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H15" t="str"/>
+      <x:c r="I15" t="str"/>
+      <x:c r="J15" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="31" t="str"/>
@@ -1054,6 +1158,11 @@
       <x:c r="G16" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H16" t="str"/>
+      <x:c r="I16" t="str"/>
+      <x:c r="J16" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="31" t="str"/>
@@ -1065,6 +1174,11 @@
       <x:c r="G17" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H17" t="str"/>
+      <x:c r="I17" t="str"/>
+      <x:c r="J17" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="31" t="str"/>
@@ -1076,6 +1190,11 @@
       <x:c r="G18" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H18" t="str"/>
+      <x:c r="I18" t="str"/>
+      <x:c r="J18" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="31" t="str"/>
@@ -1087,6 +1206,11 @@
       <x:c r="G19" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H19" t="str"/>
+      <x:c r="I19" t="str"/>
+      <x:c r="J19" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="31" t="str"/>
@@ -1098,6 +1222,11 @@
       <x:c r="G20" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H20" t="str"/>
+      <x:c r="I20" t="str"/>
+      <x:c r="J20" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="31" t="str"/>
@@ -1109,6 +1238,11 @@
       <x:c r="G21" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H21" t="str"/>
+      <x:c r="I21" t="str"/>
+      <x:c r="J21" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="31" t="str"/>
@@ -1120,6 +1254,11 @@
       <x:c r="G22" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H22" t="str"/>
+      <x:c r="I22" t="str"/>
+      <x:c r="J22" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="31" t="str"/>
@@ -1131,6 +1270,11 @@
       <x:c r="G23" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H23" t="str"/>
+      <x:c r="I23" t="str"/>
+      <x:c r="J23" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="31" t="str"/>
@@ -1142,6 +1286,11 @@
       <x:c r="G24" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H24" t="str"/>
+      <x:c r="I24" t="str"/>
+      <x:c r="J24" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="31" t="str"/>
@@ -1153,6 +1302,11 @@
       <x:c r="G25" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H25" t="str"/>
+      <x:c r="I25" t="str"/>
+      <x:c r="J25" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="31" t="str"/>
@@ -1164,6 +1318,11 @@
       <x:c r="G26" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H26" t="str"/>
+      <x:c r="I26" t="str"/>
+      <x:c r="J26" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="31" t="str"/>
@@ -1175,6 +1334,11 @@
       <x:c r="G27" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H27" t="str"/>
+      <x:c r="I27" t="str"/>
+      <x:c r="J27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="31" t="str"/>
@@ -1186,6 +1350,11 @@
       <x:c r="G28" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H28" t="str"/>
+      <x:c r="I28" t="str"/>
+      <x:c r="J28" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="31" t="str"/>
@@ -1197,6 +1366,11 @@
       <x:c r="G29" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H29" t="str"/>
+      <x:c r="I29" t="str"/>
+      <x:c r="J29" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="31" t="str"/>
@@ -1208,6 +1382,11 @@
       <x:c r="G30" s="33" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H30" t="str"/>
+      <x:c r="I30" t="str"/>
+      <x:c r="J30" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="39" t="str"/>
@@ -1219,6 +1398,11 @@
       <x:c r="G31" s="41" t="str">
         <x:v>Oui</x:v>
       </x:c>
+      <x:c r="H31" t="str"/>
+      <x:c r="I31" t="str"/>
+      <x:c r="J31" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
@@ -1228,7 +1412,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73be81034ed74246"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1e745deb1c84da2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5519,7 +5703,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1c62b865aa44c19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffda02ed678b40cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8007,7 +8191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf97fccff324147e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b3b9211a6454d77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
